--- a/src/fungi_pipeline/excel/fungal_summary.xlsx
+++ b/src/fungi_pipeline/excel/fungal_summary.xlsx
@@ -33,7 +33,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,11 @@
         <fgColor rgb="00FF6347"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0087CEFA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -63,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -77,6 +82,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -445,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:AD14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -474,11 +482,13 @@
     <col width="16" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
-      <c r="B1" t="inlineStr"/>
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>AMR</t>
@@ -511,82 +521,97 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Biofilm</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Biofilm</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Biofilm</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Biofilm</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Biofilm</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Biofilm</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Biofilm</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Biofilm</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Bio</t>
+          <t>Biofilm</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Hpat</t>
+          <t>H-pat</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Hpat</t>
+          <t>H-pat</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>H-pat</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>H-pat</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>Thermophile</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>Rad-res</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>Spore</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Spore</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Spore</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Spore</t>
         </is>
       </c>
     </row>
@@ -603,213 +628,497 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>ERG11-Candida-albicans</t>
+          <t>ERG11</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>CDR1-Candida-albicans</t>
+          <t>CDR1</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>MDR1-Candida-albicans</t>
+          <t>MDR1</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>UPC2-Candida-albicans</t>
+          <t>UPC2</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>TAC1-Candida-albicans</t>
+          <t>TAC1</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>MRR1-Candida-albicans</t>
+          <t>MRR1</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>BCR1-Candida-albicans</t>
+          <t>BCR1</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>EFG1-Candida-albicans</t>
+          <t>EFG1</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>TEC1-Candida-albicans</t>
+          <t>TEC1</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr">
         <is>
-          <t>HWP1-Candida-albicans</t>
+          <t>HWP1</t>
         </is>
       </c>
       <c r="M2" s="1" t="inlineStr">
         <is>
-          <t>ALS3-Candida-albicans</t>
+          <t>ALS3</t>
         </is>
       </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>NDT80-Candida-albicans</t>
+          <t>NDT80</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>ERG251-Candida-albicans</t>
+          <t>ERG251</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
         <is>
-          <t>CZF1-Candida-albicans</t>
+          <t>CZF1</t>
         </is>
       </c>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>FLO8-Candida-albicans</t>
+          <t>FLO8</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr">
         <is>
-          <t>SAP5-Candida-albicans</t>
+          <t>SAP5</t>
         </is>
       </c>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>RIM101-Candida-albicans</t>
+          <t>PLB1</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr">
         <is>
-          <t>HSP90-Aspergillus-fumigatus</t>
+          <t>LAC1</t>
         </is>
       </c>
       <c r="U2" s="1" t="inlineStr">
         <is>
-          <t>brlA-Emericella-nidulans</t>
+          <t>RIM101</t>
         </is>
       </c>
       <c r="V2" s="1" t="inlineStr">
         <is>
-          <t>abaA-Emericella-nidulans</t>
+          <t>HSP90</t>
         </is>
       </c>
       <c r="W2" s="1" t="inlineStr">
         <is>
-          <t>wetA-Emericella-nidulans</t>
+          <t>RAD51</t>
         </is>
       </c>
       <c r="X2" s="1" t="inlineStr">
         <is>
-          <t>srr1-Coprinopsis-cinerea</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
+          <t>brlA</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
+          <t>abaA</t>
+        </is>
+      </c>
+      <c r="Z2" s="1" t="inlineStr">
+        <is>
+          <t>wetA</t>
+        </is>
+      </c>
+      <c r="AA2" s="1" t="inlineStr">
+        <is>
+          <t>srr1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>r,y,r+y</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>Phylum</t>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>Phyla</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Candida</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Candida</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Candida</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Candida</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>Candida</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>Candida</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>Candida</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>Candida</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>Candida</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>Candida</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Candida</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>Candida</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>Candida</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>Candida</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>Candida</t>
+        </is>
+      </c>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>Candida</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>Cryptococcus</t>
+        </is>
+      </c>
+      <c r="T3" s="1" t="inlineStr">
+        <is>
+          <t>Cryptococcus</t>
+        </is>
+      </c>
+      <c r="U3" s="1" t="inlineStr">
+        <is>
+          <t>Candida</t>
+        </is>
+      </c>
+      <c r="V3" s="1" t="inlineStr">
+        <is>
+          <t>Aspergillus</t>
+        </is>
+      </c>
+      <c r="W3" s="1" t="inlineStr">
+        <is>
+          <t>Saccharomyces</t>
+        </is>
+      </c>
+      <c r="X3" s="1" t="inlineStr">
+        <is>
+          <t>Emericella</t>
+        </is>
+      </c>
+      <c r="Y3" s="1" t="inlineStr">
+        <is>
+          <t>Emericella</t>
+        </is>
+      </c>
+      <c r="Z3" s="1" t="inlineStr">
+        <is>
+          <t>Emericella</t>
+        </is>
+      </c>
+      <c r="AA3" s="1" t="inlineStr">
+        <is>
+          <t>Coprinopsis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Albicans</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Albicans</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Albicans</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Albicans</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Albicans</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>Albicans</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>Albicans</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>Albicans</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>Albicans</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>Albicans</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>Albicans</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>Albicans</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>Albicans</t>
+        </is>
+      </c>
+      <c r="P4" s="1" t="inlineStr">
+        <is>
+          <t>Albicans</t>
+        </is>
+      </c>
+      <c r="Q4" s="1" t="inlineStr">
+        <is>
+          <t>Albicans</t>
+        </is>
+      </c>
+      <c r="R4" s="1" t="inlineStr">
+        <is>
+          <t>Albicans</t>
+        </is>
+      </c>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>Neoformans</t>
+        </is>
+      </c>
+      <c r="T4" s="1" t="inlineStr">
+        <is>
+          <t>Neoformans</t>
+        </is>
+      </c>
+      <c r="U4" s="1" t="inlineStr">
+        <is>
+          <t>Albicans</t>
+        </is>
+      </c>
+      <c r="V4" s="1" t="inlineStr">
+        <is>
+          <t>Fumigatus</t>
+        </is>
+      </c>
+      <c r="W4" s="1" t="inlineStr">
+        <is>
+          <t>Cerevisiae</t>
+        </is>
+      </c>
+      <c r="X4" s="1" t="inlineStr">
+        <is>
+          <t>Nidulans</t>
+        </is>
+      </c>
+      <c r="Y4" s="1" t="inlineStr">
+        <is>
+          <t>Nidulans</t>
+        </is>
+      </c>
+      <c r="Z4" s="1" t="inlineStr">
+        <is>
+          <t>Nidulans</t>
+        </is>
+      </c>
+      <c r="AA4" s="1" t="inlineStr">
+        <is>
+          <t>Cinerea</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Yamadazyma tenuis</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C5" s="5" t="n">
         <v>71.8</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D5" s="5" t="n">
         <v>69.8</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E5" s="5" t="n">
         <v>55.9</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F5" s="5" t="n">
         <v>58.7</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G5" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H5" s="5" t="n">
         <v>51.2</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I5" s="6" t="n">
         <v>85.5</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J5" s="5" t="n">
         <v>51.7</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="K5" s="5" t="n">
         <v>58.1</v>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="L5" s="5" t="n">
         <v>52.7</v>
       </c>
-      <c r="M3" s="5" t="n">
+      <c r="M5" s="5" t="n">
         <v>41.5</v>
       </c>
-      <c r="N3" s="5" t="n">
+      <c r="N5" s="5" t="n">
         <v>63.8</v>
       </c>
-      <c r="O3" s="5" t="n">
+      <c r="O5" s="5" t="n">
         <v>66.8</v>
       </c>
-      <c r="P3" s="5" t="n">
+      <c r="P5" s="5" t="n">
         <v>59.6</v>
       </c>
-      <c r="Q3" s="5" t="n">
+      <c r="Q5" s="5" t="n">
         <v>38.7</v>
       </c>
-      <c r="R3" s="5" t="n">
+      <c r="R5" s="5" t="n">
         <v>37.6</v>
       </c>
-      <c r="S3" s="5" t="n">
+      <c r="S5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="5" t="n">
         <v>68.8</v>
       </c>
-      <c r="T3" s="5" t="n">
+      <c r="V5" s="5" t="n">
         <v>74.5</v>
       </c>
-      <c r="U3" s="5" t="n">
+      <c r="W5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="V3" s="5" t="n">
+      <c r="Y5" s="5" t="n">
         <v>47.7</v>
       </c>
-      <c r="W3" s="5" t="n">
+      <c r="Z5" s="5" t="n">
         <v>40.6</v>
       </c>
-      <c r="X3" s="5" t="n">
+      <c r="AA5" s="5" t="n">
         <v>44.4</v>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>1,21,22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>Ascomycota</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Summary Statistics</t>
         </is>

--- a/src/fungi_pipeline/excel/fungal_summary.xlsx
+++ b/src/fungi_pipeline/excel/fungal_summary.xlsx
@@ -47,12 +47,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF6347"/>
+        <fgColor rgb="0087CEFA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0087CEFA"/>
+        <fgColor rgb="00FF6347"/>
       </patternFill>
     </fill>
   </fills>
@@ -68,13 +68,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -87,6 +87,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -453,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD14"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1024,86 +1025,86 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Yamadazyma tenuis</t>
+          <t>Alternaria arborescens</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>71.8</v>
+        <v>46.1</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>69.8</v>
+        <v>48.6</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>55.9</v>
+        <v>37.9</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>58.7</v>
+        <v>52.3</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>49</v>
+        <v>44.8</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>85.5</v>
+        <v>44.2</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>65</v>
       </c>
       <c r="J5" s="5" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5" t="n">
         <v>51.7</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v>66.8</v>
-      </c>
       <c r="P5" s="5" t="n">
-        <v>59.6</v>
+        <v>60.5</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="R5" s="5" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="S5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="7" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="T5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="V5" s="5" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="W5" s="7" t="n">
-        <v>0</v>
+        <v>69.59999999999999</v>
+      </c>
+      <c r="V5" s="7" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="W5" s="5" t="n">
+        <v>69.2</v>
       </c>
       <c r="X5" s="5" t="n">
-        <v>60</v>
+        <v>50.8</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>47.7</v>
+        <v>40</v>
       </c>
       <c r="Z5" s="5" t="n">
-        <v>40.6</v>
+        <v>66.7</v>
       </c>
       <c r="AA5" s="5" t="n">
-        <v>44.4</v>
+        <v>37.1</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1118,79 +1119,2863 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Aspergillus lentulus</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="T6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="V6" s="7" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="W6" s="5" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="X6" s="5" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="Y6" s="5" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="Z6" s="5" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="AA6" s="5" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>1,20,21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Aspergillus pseudoviridinutans</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="T7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="V7" s="7" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="W7" s="5" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="X7" s="5" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="Y7" s="5" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="Z7" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>1,20,21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Colletotrichum fructicola</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="O8" s="5" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="T8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="V8" s="7" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="W8" s="5" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="X8" s="5" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="Y8" s="5" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="Z8" s="5" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="AA8" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>1,21,22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Colletotrichum gloeosporioides</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="5" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="R9" s="5" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="S9" s="5" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="T9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="5" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="V9" s="7" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="W9" s="5" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="X9" s="5" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="Y9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="5" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="AA9" s="5" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>1,20,21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Collybia sordida</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="U10" s="5" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="V10" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="W10" s="5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="X10" s="5" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="Y10" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z10" s="5" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="AA10" s="5" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0,19,19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Basidiomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Cryphonectria parasitica</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="5" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="T11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="7" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="V11" s="7" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="W11" s="5" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="X11" s="5" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="Y11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="5" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="AA11" s="5" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2,19,21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Fomitopsis pinicola</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="O12" s="5" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="5" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="T12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="V12" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="W12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="Y12" s="5" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="Z12" s="5" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="AA12" s="5" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>1,19,20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Basidiomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Fusarium mangiferae</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="T13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="5" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="V13" s="7" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="W13" s="5" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="X13" s="5" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="Y13" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z13" s="5" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AA13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>1,21,22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Fusarium proliferatum</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="5" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="T14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="5" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="V14" s="7" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="W14" s="5" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="X14" s="5" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="Y14" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="Z14" s="5" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AA14" s="5" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>1,22,23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Gaeumannomyces tritici</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="S15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="5" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="V15" s="7" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="W15" s="5" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="X15" s="5" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="Y15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="AA15" s="5" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>1,17,18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Grifola frondosa</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="V16" s="5" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="W16" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="X16" s="5" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="Y16" s="5" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="Z16" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA16" s="5" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>0,18,18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Basidiomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Grosmannia clavigera</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="R17" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="S17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="5" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="V17" s="7" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="W17" s="5" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="X17" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="Y17" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z17" s="5" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="AA17" s="5" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>1,19,20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Macrophomina phaseolina</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="T18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="V18" s="7" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="W18" s="5" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="X18" s="5" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="Y18" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z18" s="5" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="AA18" s="5" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>1,23,24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Metarhizium brunneum</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="5" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="T19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="5" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="V19" s="7" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="W19" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="X19" s="5" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="Y19" s="5" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="Z19" s="5" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AA19" s="5" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>1,20,21</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Neurospora crassa</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="5" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="T20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="V20" s="7" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="W20" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="X20" s="5" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="Y20" s="5" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="Z20" s="5" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="AA20" s="5" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1,18,19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Penicillium camemberti</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="Q21" s="5" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="5" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="T21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="5" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="V21" s="7" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="W21" s="5" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="X21" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="Y21" s="5" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="Z21" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA21" s="5" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>1,21,22</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Penicillium chrysogenum</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="P22" s="5" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="Q22" s="5" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="5" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="V22" s="7" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="W22" s="5" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="X22" s="5" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="Y22" s="5" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="Z22" s="5" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="AA22" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>1,21,22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Penicillium digitatum</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="Q23" s="5" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="5" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="V23" s="7" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="W23" s="5" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="X23" s="5" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="Y23" s="5" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="Z23" s="5" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="AA23" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>1,20,21</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Pyricularia oryzae</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="5" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="T24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="5" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="V24" s="7" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="W24" s="5" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="X24" s="5" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="Y24" s="5" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Z24" s="5" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="AA24" s="5" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>1,20,21</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Rosellinia necatrix</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="5" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="P25" s="5" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Q25" s="5" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="R25" s="5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="S25" s="5" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="T25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="5" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="V25" s="7" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="W25" s="5" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="X25" s="5" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="Y25" s="5" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="Z25" s="5" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="AA25" s="5" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>2,18,20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Saccharomyces cerevisiae</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="5" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="V26" s="7" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="W26" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="X26" s="5" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="Y26" s="5" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="Z26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="5" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>2,18,20</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Saccharomyces paradoxus</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="M27" s="5" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="N27" s="5" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="O27" s="5" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="P27" s="5" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="5" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="U27" s="5" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="V27" s="5" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="W27" s="7" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="X27" s="5" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="Y27" s="5" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="Z27" s="5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="AA27" s="5" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>2,20,22</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sclerotinia sclerotiorum</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="M28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="O28" s="5" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="P28" s="5" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="Q28" s="5" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="5" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="T28" s="5" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="U28" s="5" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="V28" s="7" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="W28" s="5" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="X28" s="5" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="Y28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="5" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="AA28" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>1,21,22</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sodiomyces alkalinus</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="O29" s="5" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="P29" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q29" s="5" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="5" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="V29" s="7" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="W29" s="5" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="X29" s="5" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="Y29" s="5" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="Z29" s="5" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AA29" s="5" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>2,18,20</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Tolypocladium ophioglossoides</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="5" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="V30" s="7" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="W30" s="5" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="X30" s="5" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="Y30" s="5" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="Z30" s="5" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AA30" s="5" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>1,17,18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Trichoderma reesei</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="M31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="Q31" s="5" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="5" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="T31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="V31" s="7" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="W31" s="5" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="X31" s="5" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="Y31" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z31" s="5" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="AA31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>1,18,19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Tuber aestivum</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="L32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="5" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="V32" s="7" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="W32" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="X32" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="Y32" s="5" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="Z32" s="5" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="AA32" s="5" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>1,20,21</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Ustilaginoidea virens</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="Q33" s="5" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="5" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="T33" s="5" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="U33" s="5" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="V33" s="7" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="W33" s="5" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="X33" s="5" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="Y33" s="5" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="Z33" s="5" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="AA33" s="5" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>2,21,23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Zygosaccharomyces bailii</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="S34" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="T34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="5" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="V34" s="5" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="W34" s="7" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="X34" s="5" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="Y34" s="5" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="Z34" s="5" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="AA34" s="5" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>2,21,23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>Ascomycota</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>Summary Statistics</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Total organisms</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="B36" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Rows with ≥1 red cell</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="B37" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Rows with ≥1 yellow (no red)</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Completely blue rows</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>% with red</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="B41" t="n">
+        <v>93.3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>% with yellow</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="B42" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>% completely blue</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B43" t="n">
         <v>0</v>
       </c>
     </row>
